--- a/data/excel/Administration_AvenueManagement_ManageCostCenter.xlsx
+++ b/data/excel/Administration_AvenueManagement_ManageCostCenter.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CD5438-2BBF-4EF7-8BA2-2C895E144635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396EAEB6-7532-458D-B3DD-3BF826F6CDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,27 +55,12 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Verify Corporate Profiling</t>
-  </si>
-  <si>
-    <t>Piyush_QL</t>
-  </si>
-  <si>
-    <t>Password@123456</t>
-  </si>
-  <si>
     <t>CSName</t>
   </si>
   <si>
     <t>CSCode</t>
   </si>
   <si>
-    <t>QA Cost Center</t>
-  </si>
-  <si>
-    <t>C001</t>
-  </si>
-  <si>
     <t>CBranchQty</t>
   </si>
   <si>
@@ -83,6 +68,21 @@
   </si>
   <si>
     <t>Delhi travels,laxmi travel,QLABS Agency,MSR Travels</t>
+  </si>
+  <si>
+    <t>Piyush_ql</t>
+  </si>
+  <si>
+    <t>EE6B4B@E7</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>Manager Cost Center</t>
+  </si>
+  <si>
+    <t>Verify Manage Cost Centre</t>
   </si>
 </sst>
 </file>
@@ -176,9 +176,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -469,7 +473,7 @@
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -499,16 +503,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -516,7 +520,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -527,42 +531,44 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"at,qlabs12345"</formula1>
+  <dataValidations disablePrompts="1" count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{5F4EF7C0-E937-453A-B675-6351DB67A75F}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"Piyush_QL"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{81539D14-6750-4E74-B332-1E77F87E6E22}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Password@123456"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{250CEC3F-ACD8-4757-B55B-A2BCD60FD794}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{C37B0A0B-AA4C-4AD6-B04E-A3DF8B50815C}">
+      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{18955B78-9E54-4A56-9BD6-50AE77CDD701}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>